--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 01/01. Báo giá bảo hành/BG_AnhTruc_120126.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 01/01. Báo giá bảo hành/BG_AnhTruc_120126.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 01\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2005DC28-A93B-4433-8C03-3847DDC13319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
@@ -18,12 +17,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$23</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -119,16 +118,19 @@
   </si>
   <si>
     <t>0032002BDA</t>
+  </si>
+  <si>
+    <t>KH không sửa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,6 +224,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -381,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -478,6 +486,63 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -502,67 +567,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -638,9 +649,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -678,9 +689,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -715,7 +726,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -750,7 +761,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -923,7 +934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -946,82 +957,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="52" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="54"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="51"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="55" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="57"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="58" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="60"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="21"/>
@@ -1032,11 +1043,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1046,11 +1057,11 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
@@ -1063,11 +1074,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -1144,17 +1155,17 @@
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
       <c r="J12" s="8">
         <f>SUM(J11:J11)</f>
         <v>1155000</v>
@@ -1179,7 +1190,9 @@
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="63" t="s">
+        <v>32</v>
+      </c>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
@@ -1297,12 +1310,12 @@
       <c r="D22" s="17"/>
       <c r="E22" s="11"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1379,11 +1392,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="14">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A5:J5"/>
@@ -1393,9 +1401,14 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0" top="1.75" bottom="0" header="0" footer="0"/>
   <pageSetup scale="28" orientation="landscape" r:id="rId2"/>
